--- a/backend/storage/output/excel/scr-train/Rail_Madad_Report_5_SCR_Train_Unsatisfactory_13-07-2026.xlsx
+++ b/backend/storage/output/excel/scr-train/Rail_Madad_Report_5_SCR_Train_Unsatisfactory_13-07-2026.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,17 +685,17 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>2026071213571</t>
+          <t>2026071312664</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 23:20</t>
+          <t>13-07-26 22:40</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>07425</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Coach - Cleanliness</t>
+          <t>Bed Roll</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Dirty / Torn</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2026071211909</t>
+          <t>2026071311765</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 21:21</t>
+          <t>13-07-26 21:32</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>07053</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Coach Interior</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
@@ -779,17 +779,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2026071209786</t>
+          <t>2026071312194</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 18:51</t>
+          <t>13-07-26 22:05</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2026071209631</t>
+          <t>2026071311837</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 18:38</t>
+          <t>13-07-26 21:38</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2026071208819</t>
+          <t>2026071311175</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 17:34</t>
+          <t>13-07-26 20:51</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Water Availability</t>
+          <t>Coach - Cleanliness</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>Packaged Drinking Water / Rail Neer</t>
+          <t>Coach Interior</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>CML</t>
+          <t>CNW</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
@@ -920,17 +920,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>2026071207815</t>
+          <t>2026071309619</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 16:02</t>
+          <t>13-07-26 19:04</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>67760</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -940,12 +940,12 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Punctuality</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2026071206620</t>
+          <t>2026071309778</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 14:09</t>
+          <t>13-07-26 19:16</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>Punctuality</t>
+          <t>Water Availability</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>Late Running</t>
+          <t>Toilet</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>CHG</t>
+          <t>CNW</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>2026071206244</t>
+          <t>2026071308888</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 13:28</t>
+          <t>13-07-26 17:58</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>07194</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>2026071205770</t>
+          <t>2026071308713</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 12:35</t>
+          <t>13-07-26 17:42</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Coach - Cleanliness</t>
+          <t>Punctuality</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Coach Interior</t>
+          <t>Late Running</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>CNW</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
@@ -1108,17 +1108,17 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>2026071204420</t>
+          <t>2026071308381</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 10:10</t>
+          <t>13-07-26 17:15</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Punctuality</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Late Running</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>CNW</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="I13" s="1" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>2026071204533</t>
+          <t>2026071307907</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 10:22</t>
+          <t>13-07-26 16:29</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>2026071204642</t>
+          <t>2026071307975</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 10:35</t>
+          <t>13-07-26 16:35</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -1249,17 +1249,17 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>2026071204200</t>
+          <t>2026071306298</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 09:45</t>
+          <t>13-07-26 13:28</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Catering &amp; Vending Services</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>RPF</t>
+          <t>CML</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>2026071202035</t>
+          <t>2026071305109</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 06:14</t>
+          <t>13-07-26 11:12</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>20629</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Coach - Cleanliness</t>
+          <t>Punctuality</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Late Running</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>CNW</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>2026071202579</t>
+          <t>2026071303914</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 07:12</t>
+          <t>13-07-26 09:08</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>20809</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>2026071201660</t>
+          <t>2026071303996</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 05:13</t>
+          <t>13-07-26 09:15</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>Coach - Cleanliness</t>
+          <t>Punctuality</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Late Running</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>CNW</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>2026071104723</t>
+          <t>2026071303935</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>11-07-26 10:27</t>
+          <t>13-07-26 09:10</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>Coach - Cleanliness</t>
+          <t>Punctuality</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Late Running</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>CNW</t>
+          <t>CHG</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>2026071200972</t>
+          <t>2026071303807</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 02:28</t>
+          <t>13-07-26 08:59</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>17016</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -1504,17 +1504,17 @@
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>Coach - Cleanliness</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>Cockroach / Rodents</t>
+          <t>Unauthorized person in Ladies/Disabled Coach/SLR/Reserve Coach</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>CNW</t>
+          <t>CML</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>2026071200488</t>
+          <t>2026071303197</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>12-07-26 01:03</t>
+          <t>13-07-26 08:08</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1551,20 +1551,443 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
+          <t>Coach - Maintenance</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>CNW</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>2026071303210</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 08:09</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>11019</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Water Availability</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Toilet</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>CNW</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>2026071302994</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 07:53</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>20809</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Water Availability</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>CNW</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>2026071302478</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 07:06</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>67764</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Punctuality</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>Late Running</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>2026071302501</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 07:08</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>17664</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Punctuality</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>Late Running</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>2026071302327</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 06:52</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>20809</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Punctuality</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>Late Running</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>2026071301898</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 06:06</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>17611</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
           <t>Coach - Cleanliness</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>Coach Interior</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Toilet</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>CNW</t>
         </is>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>2026071301541</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 04:54</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>17606</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>Theft of Passengers Belongings/Snatching</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>RPF</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>2026071301540</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 04:54</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>17664</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Punctuality</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>Late Running</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>2026071300396</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 00:51</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>07425</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Coach - Cleanliness</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>Toilet</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>CNW</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
